--- a/data/nfci_anfci_monthly.xlsx
+++ b/data/nfci_anfci_monthly.xlsx
@@ -2,21 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUFS_MATH\IdeaProjects\FOMC_Graphrag\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUFS_MATH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05963C-5F4D-4249-A9E6-153481F54B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2162F7D8-FF76-4021-A6F4-3BAD910D42BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3732" yWindow="3732" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14136" yWindow="1656" windowWidth="5892" windowHeight="8340" xr2:uid="{99580C71-6A33-4090-A61A-A7A3FB0B4C79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -234,7 +246,7 @@
     <t>2025-03</t>
   </si>
   <si>
-    <t>2025-04</t>
+    <t>2025-05</t>
   </si>
   <si>
     <t>2025-06</t>
@@ -253,6 +265,7 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -265,7 +278,7 @@
     <font>
       <sz val="8"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -303,19 +316,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -328,7 +346,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -338,44 +356,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -402,14 +420,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -436,6 +472,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -447,173 +501,152 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB796CC-C2D5-4A42-8708-F6CF25CDBB78}">
   <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="3" width="8.796875" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
@@ -627,766 +660,766 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>-0.50730389283312471</v>
-      </c>
-      <c r="C2">
-        <v>-0.41632311579536102</v>
+      <c r="B2" s="2">
+        <v>-0.49852803871379919</v>
+      </c>
+      <c r="C2" s="2">
+        <v>-0.38436342345544028</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>-0.5000334463307734</v>
-      </c>
-      <c r="C3">
-        <v>-0.427826050205588</v>
+      <c r="B3" s="2">
+        <v>-0.49138051772078167</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-0.39746972108940631</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>-0.54794590925912301</v>
-      </c>
-      <c r="C4">
-        <v>-0.49288141924163281</v>
+      <c r="B4" s="2">
+        <v>-0.54003713943400478</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-0.4641928756768543</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>-0.57519643872308757</v>
-      </c>
-      <c r="C5">
-        <v>-0.53007326309540448</v>
+      <c r="B5" s="2">
+        <v>-0.56765120451228124</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-0.49749444906397278</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>-0.58732464634966797</v>
-      </c>
-      <c r="C6">
-        <v>-0.56102421228554422</v>
+      <c r="B6" s="2">
+        <v>-0.58277260558358368</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-0.53340270793999078</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>-0.57353701442035643</v>
-      </c>
-      <c r="C7">
-        <v>-0.50886452820951422</v>
+      <c r="B7" s="2">
+        <v>-0.56628099659692177</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-0.47825607325241581</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>-0.61295469368527578</v>
-      </c>
-      <c r="C8">
-        <v>-0.62376737349638445</v>
+      <c r="B8" s="2">
+        <v>-0.60878225160340982</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.60320751875141632</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>-0.61836203779546328</v>
-      </c>
-      <c r="C9">
-        <v>-0.63588414410906702</v>
+      <c r="B9" s="2">
+        <v>-0.61457865340231199</v>
+      </c>
+      <c r="C9" s="2">
+        <v>-0.61420701919199971</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>-0.62350290278536624</v>
-      </c>
-      <c r="C10">
-        <v>-0.63869834033899076</v>
+      <c r="B10" s="2">
+        <v>-0.621491667296724</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-0.62403050559757023</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
-        <v>-0.51753465483469796</v>
-      </c>
-      <c r="C11">
-        <v>-0.49774408466669717</v>
+      <c r="B11" s="2">
+        <v>-0.51827815478661199</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-0.48075221535713281</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>-0.56864586261000927</v>
-      </c>
-      <c r="C12">
-        <v>-0.54097710456659831</v>
+      <c r="B12" s="2">
+        <v>-0.56510369725141896</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-0.51789563116614279</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>-0.55784505782944716</v>
-      </c>
-      <c r="C13">
-        <v>-0.53327032046495559</v>
+      <c r="B13" s="2">
+        <v>-0.55494946763159503</v>
+      </c>
+      <c r="C13" s="2">
+        <v>-0.50793642683298124</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
-        <v>-0.59517674901985218</v>
-      </c>
-      <c r="C14">
-        <v>-0.60917411744280492</v>
+      <c r="B14" s="2">
+        <v>-0.58698671280086023</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-0.58482491456565944</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>-0.60607050274793606</v>
-      </c>
-      <c r="C15">
-        <v>-0.63099613917835395</v>
+      <c r="B15" s="2">
+        <v>-0.60068561638911522</v>
+      </c>
+      <c r="C15" s="2">
+        <v>-0.61417481225216641</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
-        <v>-0.50695368112996619</v>
-      </c>
-      <c r="C16">
-        <v>-0.55598494573258628</v>
+      <c r="B16" s="2">
+        <v>-0.51029130763720887</v>
+      </c>
+      <c r="C16" s="2">
+        <v>-0.54393548223053179</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B17">
-        <v>-0.43654330255074919</v>
-      </c>
-      <c r="C17">
-        <v>-0.45765212239404851</v>
+      <c r="B17" s="2">
+        <v>-0.427948131461726</v>
+      </c>
+      <c r="C17" s="2">
+        <v>-0.42546011912386772</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B18">
-        <v>-0.47927008989262931</v>
-      </c>
-      <c r="C18">
-        <v>-0.49685973311276749</v>
+      <c r="B18" s="2">
+        <v>-0.46992202368341102</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-0.46676454084555852</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B19">
-        <v>-0.60354527042307882</v>
-      </c>
-      <c r="C19">
-        <v>-0.59970289331784676</v>
+      <c r="B19" s="2">
+        <v>-0.59555360547865954</v>
+      </c>
+      <c r="C19" s="2">
+        <v>-0.58287168713256376</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B20">
-        <v>-0.59942589470679142</v>
-      </c>
-      <c r="C20">
-        <v>-0.60411865096961925</v>
+      <c r="B20" s="2">
+        <v>-0.59796408717617699</v>
+      </c>
+      <c r="C20" s="2">
+        <v>-0.59513584372451656</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B21">
-        <v>-0.57649878937620325</v>
-      </c>
-      <c r="C21">
-        <v>-0.58975557810489698</v>
+      <c r="B21" s="2">
+        <v>-0.57113776618006495</v>
+      </c>
+      <c r="C21" s="2">
+        <v>-0.57479489352629076</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B22">
-        <v>-0.58344306558507275</v>
-      </c>
-      <c r="C22">
-        <v>-0.59626390504650095</v>
+      <c r="B22" s="2">
+        <v>-0.57704457495694816</v>
+      </c>
+      <c r="C22" s="2">
+        <v>-0.57981344546251523</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B23">
-        <v>-0.51750210703986521</v>
-      </c>
-      <c r="C23">
-        <v>-0.56640451281106174</v>
+      <c r="B23" s="2">
+        <v>-0.51198979518511822</v>
+      </c>
+      <c r="C23" s="2">
+        <v>-0.55207143333408171</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B24">
-        <v>-0.53378707899235045</v>
-      </c>
-      <c r="C24">
-        <v>-0.56626746679604978</v>
+      <c r="B24" s="2">
+        <v>-0.52764845926990878</v>
+      </c>
+      <c r="C24" s="2">
+        <v>-0.55199019351296719</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B25">
-        <v>-0.56054763936518648</v>
-      </c>
-      <c r="C25">
-        <v>-0.55760034489277455</v>
+      <c r="B25" s="2">
+        <v>-0.55360488528309593</v>
+      </c>
+      <c r="C25" s="2">
+        <v>-0.54060790997136754</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B26">
-        <v>-0.60738720037935578</v>
-      </c>
-      <c r="C26">
-        <v>-0.60132593139814028</v>
+      <c r="B26" s="2">
+        <v>-0.59509036200854126</v>
+      </c>
+      <c r="C26" s="2">
+        <v>-0.56940737955895848</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B27">
-        <v>9.6479441113425629E-2</v>
-      </c>
-      <c r="C27">
-        <v>0.15020331711061291</v>
+      <c r="B27" s="2">
+        <v>9.4278743830435136E-2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.16955977121811411</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B28">
-        <v>0.25870047668605672</v>
-      </c>
-      <c r="C28">
-        <v>0.35923323146819203</v>
+      <c r="B28" s="2">
+        <v>0.25971379063141498</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.36824169349541119</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B29">
-        <v>-0.35592769384920869</v>
-      </c>
-      <c r="C29">
-        <v>-0.46116150770817183</v>
+      <c r="B29" s="2">
+        <v>-0.35149601662561653</v>
+      </c>
+      <c r="C29" s="2">
+        <v>-0.46022523823917227</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
+      <c r="A30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B30">
-        <v>-0.44367341383781261</v>
-      </c>
-      <c r="C30">
-        <v>-0.51985630321918519</v>
+      <c r="B30" s="2">
+        <v>-0.42953251387135599</v>
+      </c>
+      <c r="C30" s="2">
+        <v>-0.50702087777809868</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B31">
-        <v>-0.50574619465829374</v>
-      </c>
-      <c r="C31">
-        <v>-0.69595783520927057</v>
+      <c r="B31" s="2">
+        <v>-0.49950504566334852</v>
+      </c>
+      <c r="C31" s="2">
+        <v>-0.6753941091736535</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
+      <c r="A32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B32">
-        <v>-0.5506085914579385</v>
-      </c>
-      <c r="C32">
-        <v>-0.54205683924384152</v>
+      <c r="B32" s="2">
+        <v>-0.54367649755029201</v>
+      </c>
+      <c r="C32" s="2">
+        <v>-0.51443041147395441</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
+      <c r="A33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B33">
-        <v>-0.60030102306579125</v>
-      </c>
-      <c r="C33">
-        <v>-0.53504539004735896</v>
+      <c r="B33" s="2">
+        <v>-0.59318489319511447</v>
+      </c>
+      <c r="C33" s="2">
+        <v>-0.50530397142216743</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
+      <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B34">
-        <v>-0.62243809796975724</v>
-      </c>
-      <c r="C34">
-        <v>-0.5503177412540784</v>
+      <c r="B34" s="2">
+        <v>-0.61463880757993428</v>
+      </c>
+      <c r="C34" s="2">
+        <v>-0.51264062369961105</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
+      <c r="A35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B35">
-        <v>-0.64427771341122098</v>
-      </c>
-      <c r="C35">
-        <v>-0.58760955424440253</v>
+      <c r="B35" s="2">
+        <v>-0.63892391860371478</v>
+      </c>
+      <c r="C35" s="2">
+        <v>-0.56235189321795853</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B36">
-        <v>-0.67481056279745444</v>
-      </c>
-      <c r="C36">
-        <v>-0.58905245806971585</v>
+      <c r="B36" s="2">
+        <v>-0.66616865610061693</v>
+      </c>
+      <c r="C36" s="2">
+        <v>-0.56762447503308677</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B37">
-        <v>-0.69683639271981579</v>
-      </c>
-      <c r="C37">
-        <v>-0.6144504423952325</v>
+      <c r="B37" s="2">
+        <v>-0.69083891680845344</v>
+      </c>
+      <c r="C37" s="2">
+        <v>-0.58779510572424265</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
+      <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B38">
-        <v>-0.67304857422738462</v>
-      </c>
-      <c r="C38">
-        <v>-0.61479062339580914</v>
+      <c r="B38" s="2">
+        <v>-0.67025843792862405</v>
+      </c>
+      <c r="C38" s="2">
+        <v>-0.5988662406107268</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
+      <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B39">
-        <v>-0.65652260594672174</v>
-      </c>
-      <c r="C39">
-        <v>-0.65506589667977377</v>
+      <c r="B39" s="2">
+        <v>-0.65043519612530609</v>
+      </c>
+      <c r="C39" s="2">
+        <v>-0.65691193579558704</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
+      <c r="A40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B40">
-        <v>-0.58008930455614482</v>
-      </c>
-      <c r="C40">
-        <v>-0.55785890207868549</v>
+      <c r="B40" s="2">
+        <v>-0.57613666176052003</v>
+      </c>
+      <c r="C40" s="2">
+        <v>-0.55475152289534047</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
+      <c r="A41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B41">
-        <v>-0.54673523363529275</v>
-      </c>
-      <c r="C41">
-        <v>-0.52027596761651584</v>
+      <c r="B41" s="2">
+        <v>-0.54022390008041998</v>
+      </c>
+      <c r="C41" s="2">
+        <v>-0.50883605957313727</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
+      <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B42">
-        <v>-0.55757965560315104</v>
-      </c>
-      <c r="C42">
-        <v>-0.53918670693595527</v>
+      <c r="B42" s="2">
+        <v>-0.55394141870181124</v>
+      </c>
+      <c r="C42" s="2">
+        <v>-0.53457382791870445</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B43">
-        <v>-0.38524822485785748</v>
-      </c>
-      <c r="C43">
-        <v>-0.27920848275045301</v>
+      <c r="B43" s="2">
+        <v>-0.38573219164473382</v>
+      </c>
+      <c r="C43" s="2">
+        <v>-0.26428738233820498</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B44">
-        <v>-0.28421776751857603</v>
-      </c>
-      <c r="C44">
-        <v>-0.15639853451740979</v>
+      <c r="B44" s="2">
+        <v>-0.28729044678010118</v>
+      </c>
+      <c r="C44" s="2">
+        <v>-0.14514403725510799</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B45">
-        <v>-0.194524632971559</v>
-      </c>
-      <c r="C45">
-        <v>-6.9624811541034351E-2</v>
+      <c r="B45" s="2">
+        <v>-0.19984771359335951</v>
+      </c>
+      <c r="C45" s="2">
+        <v>-6.6516741527059275E-2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B46">
-        <v>-0.17969349058455461</v>
-      </c>
-      <c r="C46">
-        <v>-0.11320919421694139</v>
+      <c r="B46" s="2">
+        <v>-0.17729152059911729</v>
+      </c>
+      <c r="C46" s="2">
+        <v>-9.4202861489421474E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B47">
-        <v>-0.14458009713865411</v>
-      </c>
-      <c r="C47">
-        <v>-0.16017015451055061</v>
+      <c r="B47" s="2">
+        <v>-0.16291503235764099</v>
+      </c>
+      <c r="C47" s="2">
+        <v>-0.1762788459004255</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
+      <c r="A48" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B48">
-        <v>-0.16193303933702949</v>
-      </c>
-      <c r="C48">
-        <v>-0.17540241751173599</v>
+      <c r="B48" s="2">
+        <v>-0.16529571292325571</v>
+      </c>
+      <c r="C48" s="2">
+        <v>-0.1742645179539985</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
+      <c r="A49" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B49">
-        <v>-0.1967417459471888</v>
-      </c>
-      <c r="C49">
-        <v>-0.20886048294520479</v>
+      <c r="B49" s="2">
+        <v>-0.19435213479098401</v>
+      </c>
+      <c r="C49" s="2">
+        <v>-0.198579639177733</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
+      <c r="A50" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B50">
-        <v>-0.29767015620907072</v>
-      </c>
-      <c r="C50">
-        <v>-0.29551250191518169</v>
+      <c r="B50" s="2">
+        <v>-0.29880713754440719</v>
+      </c>
+      <c r="C50" s="2">
+        <v>-0.28821944144411549</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
+      <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B51">
-        <v>-0.1837117544829196</v>
-      </c>
-      <c r="C51">
-        <v>-0.15167087828675579</v>
+      <c r="B51" s="2">
+        <v>-0.1957341440104727</v>
+      </c>
+      <c r="C51" s="2">
+        <v>-0.142911032453893</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
+      <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B52">
-        <v>-0.208291952752302</v>
-      </c>
-      <c r="C52">
-        <v>-0.23801989075553079</v>
+      <c r="B52" s="2">
+        <v>-0.20869241668427371</v>
+      </c>
+      <c r="C52" s="2">
+        <v>-0.22465029972017581</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
+      <c r="A53" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B53">
-        <v>-0.22142359357954461</v>
-      </c>
-      <c r="C53">
-        <v>-0.23817962483149899</v>
+      <c r="B53" s="2">
+        <v>-0.21865122561487371</v>
+      </c>
+      <c r="C53" s="2">
+        <v>-0.22243460273105781</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
+      <c r="A54" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B54">
-        <v>-0.25993003429323869</v>
-      </c>
-      <c r="C54">
-        <v>-0.26232840224028131</v>
+      <c r="B54" s="2">
+        <v>-0.25893255751902178</v>
+      </c>
+      <c r="C54" s="2">
+        <v>-0.24671259344983551</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
+      <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B55">
-        <v>-0.33201717586914398</v>
-      </c>
-      <c r="C55">
-        <v>-0.2837759021008302</v>
+      <c r="B55" s="2">
+        <v>-0.3361573064206087</v>
+      </c>
+      <c r="C55" s="2">
+        <v>-0.26796208521498133</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
+      <c r="A56" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B56">
-        <v>-0.30558318853660249</v>
-      </c>
-      <c r="C56">
-        <v>-0.32609654536323268</v>
+      <c r="B56" s="2">
+        <v>-0.30620167077238553</v>
+      </c>
+      <c r="C56" s="2">
+        <v>-0.31414368238964802</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
+      <c r="A57" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B57">
-        <v>-0.35166780900425498</v>
-      </c>
-      <c r="C57">
-        <v>-0.38090610634109218</v>
+      <c r="B57" s="2">
+        <v>-0.34627047827242818</v>
+      </c>
+      <c r="C57" s="2">
+        <v>-0.36896449335026371</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
+      <c r="A58" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B58">
-        <v>-0.38925425285163873</v>
-      </c>
-      <c r="C58">
-        <v>-0.41988658381659172</v>
+      <c r="B58" s="2">
+        <v>-0.38834753712674769</v>
+      </c>
+      <c r="C58" s="2">
+        <v>-0.42147558653359202</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
+      <c r="A59" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B59">
-        <v>-0.4383244821910604</v>
-      </c>
-      <c r="C59">
-        <v>-0.48039192124528818</v>
+      <c r="B59" s="2">
+        <v>-0.4374348412724835</v>
+      </c>
+      <c r="C59" s="2">
+        <v>-0.47284326695546203</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
+      <c r="A60" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B60">
-        <v>-0.41513731331536857</v>
-      </c>
-      <c r="C60">
-        <v>-0.42650343625059223</v>
+      <c r="B60" s="2">
+        <v>-0.41515300047913251</v>
+      </c>
+      <c r="C60" s="2">
+        <v>-0.41631998916666169</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
+      <c r="A61" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B61">
-        <v>-0.39566274599817869</v>
-      </c>
-      <c r="C61">
-        <v>-0.38669750665248631</v>
+      <c r="B61" s="2">
+        <v>-0.39557365061373789</v>
+      </c>
+      <c r="C61" s="2">
+        <v>-0.37029571331329603</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
+      <c r="A62" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B62">
-        <v>-0.37266326569796548</v>
-      </c>
-      <c r="C62">
-        <v>-0.36958798380666402</v>
+      <c r="B62" s="2">
+        <v>-0.37258480929183402</v>
+      </c>
+      <c r="C62" s="2">
+        <v>-0.35457570448185949</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A63" t="s">
+      <c r="A63" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B63">
-        <v>-0.41992075239007182</v>
-      </c>
-      <c r="C63">
-        <v>-0.45952720979027201</v>
+      <c r="B63" s="2">
+        <v>-0.41856853944429617</v>
+      </c>
+      <c r="C63" s="2">
+        <v>-0.44843872307108679</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
+      <c r="A64" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B64">
-        <v>-0.46768793233288442</v>
-      </c>
-      <c r="C64">
-        <v>-0.5190234253104512</v>
+      <c r="B64" s="2">
+        <v>-0.46245957702826868</v>
+      </c>
+      <c r="C64" s="2">
+        <v>-0.51292838199437474</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
+      <c r="A65" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B65">
-        <v>-0.48365480388066501</v>
-      </c>
-      <c r="C65">
-        <v>-0.51758953082993542</v>
+      <c r="B65" s="2">
+        <v>-0.48150996096641951</v>
+      </c>
+      <c r="C65" s="2">
+        <v>-0.50999044668013194</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
+      <c r="A66" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B66">
-        <v>-0.50296111416444855</v>
-      </c>
-      <c r="C66">
-        <v>-0.52279411036780976</v>
+      <c r="B66" s="2">
+        <v>-0.4994389788239878</v>
+      </c>
+      <c r="C66" s="2">
+        <v>-0.51689906482891734</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
+      <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B67">
-        <v>-0.43801077507296582</v>
-      </c>
-      <c r="C67">
-        <v>-0.44875999969167518</v>
+      <c r="B67" s="2">
+        <v>-0.43715362400539087</v>
+      </c>
+      <c r="C67" s="2">
+        <v>-0.43122962740877052</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
+      <c r="A68" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B68">
-        <v>-0.38885859262352029</v>
-      </c>
-      <c r="C68">
-        <v>-0.41153322649534652</v>
+      <c r="B68" s="2">
+        <v>-0.43036692855295777</v>
+      </c>
+      <c r="C68" s="2">
+        <v>-0.4467030405241878</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
+      <c r="A69" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B69">
-        <v>-0.48583190741619481</v>
-      </c>
-      <c r="C69">
-        <v>-0.48146504897796832</v>
+      <c r="B69" s="2">
+        <v>-0.48568826960674383</v>
+      </c>
+      <c r="C69" s="2">
+        <v>-0.47730734395071017</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A70" t="s">
+      <c r="A70" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B70">
-        <v>-0.518940113683513</v>
-      </c>
-      <c r="C70">
-        <v>-0.50011602933495181</v>
+      <c r="B70" s="2">
+        <v>-0.51118890740524947</v>
+      </c>
+      <c r="C70" s="2">
+        <v>-0.49893579732687998</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>